--- a/web/public/jeoksan/재료표_건축.xlsx
+++ b/web/public/jeoksan/재료표_건축.xlsx
@@ -2586,7 +2586,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K-건설맵  https://k-conmap.com   무료입니다.</t>
+          <t>K-건설맵  https://k-conmap.com</t>
         </is>
       </c>
     </row>

--- a/web/public/jeoksan/재료표_건축.xlsx
+++ b/web/public/jeoksan/재료표_건축.xlsx
@@ -2586,7 +2586,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K-건설맵  https://k-conmap.com</t>
+          <t>K-건설맵  https://k-conmap.com   무료입니다.</t>
         </is>
       </c>
     </row>
